--- a/app/database/MSI_database_V1.1.xlsx
+++ b/app/database/MSI_database_V1.1.xlsx
@@ -56,7 +56,7 @@
     <t>Na+ Isotope</t>
   </si>
   <si>
-    <t>IS</t>
+    <t>Lipid standard</t>
   </si>
   <si>
     <t>PC 33:1 d7</t>
